--- a/物品清单/电赛库存清单_template.xlsx
+++ b/物品清单/电赛库存清单_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MDLZ\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MDLZ\Desktop\nwpu-nuedc\物品清单\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E88403-3E39-4ACD-A6FA-EB4591576F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731DB39B-EDAA-4639-B9A9-0F1DDF441E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -1435,22 +1435,22 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:Y217"/>
-  <sheetFormatPr defaultRowHeight="14.1" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="15.625" style="202" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.5" style="202" customWidth="1"/>
-    <col min="3" max="3" width="25.75" style="202" customWidth="1"/>
-    <col min="4" max="4" width="64.125" style="202" customWidth="1"/>
-    <col min="5" max="5" width="12.5" style="203" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" style="204" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" style="202" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.453125" style="202" customWidth="1"/>
+    <col min="3" max="3" width="25.7265625" style="202" customWidth="1"/>
+    <col min="4" max="4" width="64.08984375" style="202" customWidth="1"/>
+    <col min="5" max="5" width="12.453125" style="203" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" style="204" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25" style="202" customWidth="1"/>
-    <col min="8" max="8" width="29.25" style="205" customWidth="1"/>
-    <col min="9" max="9" width="44.875" style="202" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="48.875" style="202" customWidth="1"/>
-    <col min="11" max="11" width="14.75" style="202" customWidth="1"/>
-    <col min="12" max="12" width="14.75" style="206" customWidth="1"/>
-    <col min="13" max="14" width="12.25" style="202" customWidth="1"/>
-    <col min="15" max="25" width="8.75" style="202"/>
+    <col min="8" max="8" width="29.26953125" style="205" customWidth="1"/>
+    <col min="9" max="9" width="44.90625" style="202" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="48.90625" style="202" customWidth="1"/>
+    <col min="11" max="11" width="14.7265625" style="202" customWidth="1"/>
+    <col min="12" max="12" width="14.7265625" style="206" customWidth="1"/>
+    <col min="13" max="14" width="12.26953125" style="202" customWidth="1"/>
+    <col min="15" max="25" width="8.7265625" style="202"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="197" customFormat="1" ht="15" customHeight="1">
@@ -1593,8 +1593,8 @@
       <c r="G6" s="34"/>
       <c r="H6" s="37"/>
       <c r="I6" s="38"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="24"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="39"/>
       <c r="L6" s="26"/>
       <c r="M6" s="24"/>
       <c r="N6" s="24"/>
@@ -1611,8 +1611,6 @@
       <c r="I7" s="38"/>
       <c r="J7" s="23"/>
       <c r="K7" s="24"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="39"/>
       <c r="N7" s="24"/>
     </row>
     <row r="8" spans="1:25" ht="15" customHeight="1">
@@ -4629,22 +4627,8 @@
     </row>
   </sheetData>
   <phoneticPr fontId="33" type="noConversion"/>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"云A顺丰,云A菜鸟,翱翔菜鸟,翱翔京东,星南邮政,海天苑菜鸟,海天苑京东,"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"郭储源,陈学知,曹军,"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="入库后在此填写库存数量" sqref="F2:F1048576 E12" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>-1</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H1048576 G12" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>"郭储源,陈学知,计算机学院科技楼（鱼组）,计算机学院（V5）,实验大楼,航海学院实验室（陈学知）,"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4654,9 +4638,9 @@
   <dimension ref="A1:AB200"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.75" customWidth="1"/>
-    <col min="2" max="2" width="66.75" customWidth="1"/>
-    <col min="3" max="28" width="13.75" customWidth="1"/>
+    <col min="1" max="1" width="13.7265625" customWidth="1"/>
+    <col min="2" max="2" width="66.7265625" customWidth="1"/>
+    <col min="3" max="28" width="13.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28">
